--- a/HCM/HCM -Interview master testcase document.xlsx
+++ b/HCM/HCM -Interview master testcase document.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Excel documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Excel documents\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96120B4B-1D7E-41F7-A09E-29B02790D31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3E3701-4A54-4060-84A1-09EF4029B423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{033BB443-9228-46B5-9E6E-D7BE8844FAA0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{033BB443-9228-46B5-9E6E-D7BE8844FAA0}"/>
   </bookViews>
   <sheets>
     <sheet name="interview master test document" sheetId="1" r:id="rId1"/>
@@ -25231,7 +25231,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
     </row>
-    <row r="286" spans="1:12" ht="27" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:12" ht="40.5" x14ac:dyDescent="0.35">
       <c r="A286" s="27" t="s">
         <v>199</v>
       </c>
